--- a/data/trans_bre/IP2003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,0</t>
+          <t>-10,66; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,11</t>
+          <t>-2,51; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,27</t>
+          <t>-4,14; 2,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,7</t>
+          <t>-2,08; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,06</t>
+          <t>-4,59; 4,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 114,91</t>
+          <t>-45,2; 118,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 58,67</t>
+          <t>-61,36; 67,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 154,23</t>
+          <t>-37,46; 150,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 120,09</t>
+          <t>-52,97; 112,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 14,77</t>
+          <t>-2,07; 14,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 15,88</t>
+          <t>-0,28; 15,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 4,9</t>
+          <t>-8,56; 5,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 13,1</t>
+          <t>-1,11; 13,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 83,25</t>
+          <t>-8,87; 81,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 100,2</t>
+          <t>-1,17; 99,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 30,96</t>
+          <t>-37,72; 32,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 150,88</t>
+          <t>-8,64; 143,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 13,83</t>
+          <t>-0,35; 14,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 15,4</t>
+          <t>-0,71; 15,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 8,42</t>
+          <t>-7,48; 8,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 28,41</t>
+          <t>-6,54; 25,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 56,56</t>
+          <t>-2,19; 60,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 69,4</t>
+          <t>-2,36; 71,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 41,79</t>
+          <t>-25,24; 41,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 153,93</t>
+          <t>-28,98; 139,5</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,41</t>
+          <t>0,26; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,01</t>
+          <t>0,52; 6,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,36</t>
+          <t>-2,21; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 15,36</t>
+          <t>-2,72; 14,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 50,72</t>
+          <t>1,76; 54,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 60,98</t>
+          <t>3,73; 56,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 28,76</t>
+          <t>-15,59; 31,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 117,94</t>
+          <t>-18,74; 109,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 0,0</t>
+          <t>-11,15; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,36</t>
+          <t>-2,67; 3,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,39</t>
+          <t>-4,55; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,67</t>
+          <t>-1,92; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,97</t>
+          <t>-4,01; 5,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 118,76</t>
+          <t>-48,34; 119,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 67,51</t>
+          <t>-63,12; 50,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 150,28</t>
+          <t>-34,31; 172,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 112,08</t>
+          <t>-49,38; 123,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 14,6</t>
+          <t>-2,73; 14,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 15,74</t>
+          <t>-0,25; 15,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 5,34</t>
+          <t>-8,11; 4,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 13,32</t>
+          <t>-0,45; 13,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 81,35</t>
+          <t>-10,6; 82,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 99,1</t>
+          <t>-1,76; 95,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 32,51</t>
+          <t>-36,62; 32,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 143,05</t>
+          <t>-6,54; 154,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 14,25</t>
+          <t>-0,21; 14,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 15,56</t>
+          <t>-0,77; 15,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 8,26</t>
+          <t>-6,32; 8,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 25,9</t>
+          <t>-7,39; 31,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 60,16</t>
+          <t>-0,98; 62,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 71,73</t>
+          <t>-1,69; 69,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 41,17</t>
+          <t>-22,35; 40,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 139,5</t>
+          <t>-31,69; 191,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,87</t>
+          <t>0,21; 6,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,54</t>
+          <t>0,55; 6,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,65</t>
+          <t>-2,56; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 14,44</t>
+          <t>-2,53; 14,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 54,34</t>
+          <t>0,72; 51,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 56,25</t>
+          <t>3,73; 58,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 31,91</t>
+          <t>-18,02; 33,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 109,7</t>
+          <t>-18,05; 112,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 0,0</t>
+          <t>-6,55; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 3,27</t>
+          <t>-2,73; 3,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,0</t>
+          <t>-4,14; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,74</t>
+          <t>-2,1; 4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,33</t>
+          <t>-4,64; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 119,57</t>
+          <t>-48,42; 114,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 50,67</t>
+          <t>-58,04; 58,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 172,88</t>
+          <t>-37,88; 154,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 123,51</t>
+          <t>-51,19; 136,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 14,4</t>
+          <t>-2,74; 14,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 15,39</t>
+          <t>0,53; 15,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 4,89</t>
+          <t>-8,19; 4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 13,67</t>
+          <t>-0,97; 11,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 82,44</t>
+          <t>-11,98; 83,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 95,4</t>
+          <t>1,25; 100,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 32,76</t>
+          <t>-35,45; 30,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 154,48</t>
+          <t>-7,73; 140,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>-10,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 14,88</t>
+          <t>-1,0; 13,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 15,19</t>
+          <t>0,12; 15,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 8,4</t>
+          <t>-7,2; 8,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 31,98</t>
+          <t>-11,49; 5,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 62,05</t>
+          <t>-4,48; 56,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 69,38</t>
+          <t>0,4; 69,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 40,41</t>
+          <t>-24,44; 41,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 191,16</t>
+          <t>-40,82; 30,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,64</t>
+          <t>0,31; 6,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,76</t>
+          <t>0,42; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,77</t>
+          <t>-2,84; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 14,72</t>
+          <t>-4,09; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 51,27</t>
+          <t>2,03; 50,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 58,86</t>
+          <t>2,98; 60,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 33,27</t>
+          <t>-18,73; 28,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 112,29</t>
+          <t>-24,68; 36,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,165 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.987038014902428</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-6.548318179506035</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-16,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 3,11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 2,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 4,7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 5,62</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-48,42; 114,91</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-58,04; 58,67</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-37,88; 154,23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-51,19; 136,35</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.2258956212376907</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9359786733707243</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.160421163525239</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.54478186759951</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05324716410149528</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1696524615911755</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2575587779259403</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.08144201755322454</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-8,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.732008252819157</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.142716096357085</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.102939867152243</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.639469856279351</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4841914143907822</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5804362144765202</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3787841517530615</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.511886185100847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 14,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,53; 15,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 4,9</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 11,12</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-11,98; 83,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 100,2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-35,45; 30,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 140,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.1064932638223</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.270214984322173</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.699635091731037</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.616296472603264</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.149055838376374</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.586662637691394</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.54232998130915</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.363470656172209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +785,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-10,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.84599102467793</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.843864937612629</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.627126680456337</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.122649026127562</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2693933397076992</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3917069663605726</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.08420486169058804</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4673723083137766</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 13,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 15,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 8,42</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-11,49; 5,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,48; 56,56</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 69,4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-24,44; 41,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-40,82; 30,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.742736193974164</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5292848040716537</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.194926500538896</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.9735504568420764</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1197597653803956</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.01248676127079327</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3544848573461705</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.07732769050007883</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.7657804184828</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.87621171722271</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.896126769859285</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.12407506342951</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8325489684756283</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.001980401201768</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3096208400601707</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.401796685972615</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.150314067955166</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.502045181517375</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7638757486619935</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.122060764427666</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2618419823367299</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2921933637079699</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03103742693236914</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1000036058385106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.9959515711558098</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1237788862800058</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.201275073262611</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-11.4857095168565</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04484862354396966</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.004045671284347436</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2444069705665881</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4081869399145613</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.83330195874203</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>15.39527554530582</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.418705387987917</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.035732594341309</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5656028708987202</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.693991733734611</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.417886877251816</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3025239389995213</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 6,41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,42; 7,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 3,36</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 4,08</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 50,72</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,98; 60,98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-18,73; 28,76</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-24,68; 36,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.324628704364965</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.587748087187986</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5383522527819762</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.3360304614951709</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.233455010993409</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2719654616831852</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.04150978807649428</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.02440086572934767</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3072120989258446</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4246161913253664</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.838543395074778</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.086471349054026</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.02030353417798412</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.02984557801453875</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1872563844705683</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2467927710540574</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.407003577669854</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.006575714000219</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.363627043481517</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.080924738151556</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5071966875469238</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.6098338520037379</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.287550788088451</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3627528755919204</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1083,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
